--- a/artfynd/A 20507-2020 artfynd.xlsx
+++ b/artfynd/A 20507-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1241,6 +1241,424 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114670094</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96488</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mellan Norrängen och Åvik, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>483822</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6539846</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>lågörtsgranskog med barkborreangrepp</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114670081</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96491</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mellan Norrängen och Åvik, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>483697</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6540129</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114670092</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96488</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mellan Norrängen och Åvik, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>483815</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6540028</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114670093</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5161</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mellan Norrängen och Åvik, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>483838</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6539852</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20507-2020 artfynd.xlsx
+++ b/artfynd/A 20507-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20507-2020 artfynd.xlsx
+++ b/artfynd/A 20507-2020 artfynd.xlsx
@@ -1766,7 +1766,7 @@
         <v>121142952</v>
       </c>
       <c r="B12" t="n">
-        <v>97025</v>
+        <v>97035</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 20507-2020 artfynd.xlsx
+++ b/artfynd/A 20507-2020 artfynd.xlsx
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121142952</v>
+        <v>121142951</v>
       </c>
       <c r="B12" t="n">
-        <v>97035</v>
+        <v>5189</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,31 +1779,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1811,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483822</v>
+        <v>483837</v>
       </c>
       <c r="R12" t="n">
-        <v>6539832</v>
+        <v>6539821</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,12 +1850,18 @@
           <t>2023-10-12</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1990,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121142949</v>
+        <v>121142952</v>
       </c>
       <c r="B14" t="n">
-        <v>5169</v>
+        <v>97035</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,32 +2013,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2039,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483834</v>
+        <v>483822</v>
       </c>
       <c r="R14" t="n">
-        <v>6539824</v>
+        <v>6539832</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,18 +2083,12 @@
           <t>2023-10-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121142951</v>
+        <v>121142949</v>
       </c>
       <c r="B15" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2123,21 +2123,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483837</v>
+        <v>483834</v>
       </c>
       <c r="R15" t="n">
-        <v>6539821</v>
+        <v>6539824</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 20507-2020 artfynd.xlsx
+++ b/artfynd/A 20507-2020 artfynd.xlsx
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121142950</v>
+        <v>121142952</v>
       </c>
       <c r="B13" t="n">
-        <v>4766</v>
+        <v>97048</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,32 +1896,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1929,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483835</v>
+        <v>483822</v>
       </c>
       <c r="R13" t="n">
-        <v>6539826</v>
+        <v>6539832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,18 +1966,12 @@
           <t>2023-10-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1997,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121142952</v>
+        <v>121142950</v>
       </c>
       <c r="B14" t="n">
-        <v>97035</v>
+        <v>4766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,31 +2006,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2045,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483822</v>
+        <v>483835</v>
       </c>
       <c r="R14" t="n">
-        <v>6539832</v>
+        <v>6539826</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,12 +2077,18 @@
           <t>2023-10-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20507-2020 artfynd.xlsx
+++ b/artfynd/A 20507-2020 artfynd.xlsx
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121142951</v>
+        <v>121142950</v>
       </c>
       <c r="B12" t="n">
-        <v>5189</v>
+        <v>4766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483837</v>
+        <v>483835</v>
       </c>
       <c r="R12" t="n">
-        <v>6539821</v>
+        <v>6539826</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121142952</v>
+        <v>121142949</v>
       </c>
       <c r="B13" t="n">
-        <v>97048</v>
+        <v>5169</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,31 +1896,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1928,10 +1929,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483822</v>
+        <v>483834</v>
       </c>
       <c r="R13" t="n">
-        <v>6539832</v>
+        <v>6539824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,12 +1967,18 @@
           <t>2023-10-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1990,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121142950</v>
+        <v>121142952</v>
       </c>
       <c r="B14" t="n">
-        <v>4766</v>
+        <v>97049</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,32 +2013,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2039,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483835</v>
+        <v>483822</v>
       </c>
       <c r="R14" t="n">
-        <v>6539826</v>
+        <v>6539832</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,18 +2083,12 @@
           <t>2023-10-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121142949</v>
+        <v>121142951</v>
       </c>
       <c r="B15" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2123,21 +2123,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483834</v>
+        <v>483837</v>
       </c>
       <c r="R15" t="n">
-        <v>6539824</v>
+        <v>6539821</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 20507-2020 artfynd.xlsx
+++ b/artfynd/A 20507-2020 artfynd.xlsx
@@ -1766,7 +1766,7 @@
         <v>121142950</v>
       </c>
       <c r="B12" t="n">
-        <v>4766</v>
+        <v>4769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121142949</v>
+        <v>121142951</v>
       </c>
       <c r="B13" t="n">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483834</v>
+        <v>483837</v>
       </c>
       <c r="R13" t="n">
-        <v>6539824</v>
+        <v>6539821</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,7 +2000,7 @@
         <v>121142952</v>
       </c>
       <c r="B14" t="n">
-        <v>97049</v>
+        <v>97052</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121142951</v>
+        <v>121142949</v>
       </c>
       <c r="B15" t="n">
-        <v>5189</v>
+        <v>5172</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2123,21 +2123,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483837</v>
+        <v>483834</v>
       </c>
       <c r="R15" t="n">
-        <v>6539821</v>
+        <v>6539824</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 20507-2020 artfynd.xlsx
+++ b/artfynd/A 20507-2020 artfynd.xlsx
@@ -1880,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121142951</v>
+        <v>121142949</v>
       </c>
       <c r="B13" t="n">
-        <v>5192</v>
+        <v>5172</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483837</v>
+        <v>483834</v>
       </c>
       <c r="R13" t="n">
-        <v>6539821</v>
+        <v>6539824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121142949</v>
+        <v>121142951</v>
       </c>
       <c r="B15" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2123,21 +2123,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483834</v>
+        <v>483837</v>
       </c>
       <c r="R15" t="n">
-        <v>6539824</v>
+        <v>6539821</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
